--- a/public/samples/configuration-sample.xlsx
+++ b/public/samples/configuration-sample.xlsx
@@ -19,10 +19,10 @@
     <t>NewValue</t>
   </si>
   <si>
-    <t>Date Format</t>
+    <t>Insights Cards</t>
   </si>
   <si>
-    <t>DD.MM.YYYY</t>
+    <t>Hidden</t>
   </si>
 </sst>
 </file>
